--- a/prisma/AMBIGUOUS_CASES_LOG_GENERADO.xlsx
+++ b/prisma/AMBIGUOUS_CASES_LOG_GENERADO.xlsx
@@ -643,7 +643,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>Elegibles en cribado de metadatos (E2 ≥ 0.40) pero excluidos tras análisis de texto completo (E3 &lt; 0.40)</t>
+          <t>Puntuación de relevancia E2 (informativa) ≥ 0.40 en metadatos, pero excluidos tras análisis de texto completo (E3 &lt; 0.40)</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>articulo_003349</t>
+          <t>articulo_001675</t>
         </is>
       </c>
       <c r="C7" s="15" t="n">
@@ -8689,12 +8689,12 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>"It's Not Literally True, But You Get the Gist:" How nuanced understandings of truth encourage people to condone and spread misinformation</t>
+          <t>"We are not going back" VS "Make America Great Again." The Discourse of 2024 US Presidential Campaign</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>Julia A. Langdon; Beth Anne Helgason et al.</t>
+          <t>Svitlana Kuranova; Pavlo Zernetskyi</t>
         </is>
       </c>
       <c r="F7" s="15" t="n">
@@ -8725,27 +8725,27 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>articulo_001433</t>
+          <t>articulo_003349</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Adversarial Attacks against Neural Ranking Models via In-Context Learning</t>
+          <t>"It's Not Literally True, But You Get the Gist:" How nuanced understandings of truth encourage people to condone and spread misinformation</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Amin Bigdeli; Negar Arabzadeh et al.</t>
+          <t>Julia A. Langdon; Beth Anne Helgason et al.</t>
         </is>
       </c>
       <c r="F8" s="4" t="n">
         <v>0.55</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Diferencia E2-E3: 0.2. El abstract sugería relevancia (0.55) pero el texto completo no confirmó intención comunicativa (0.35). Probable caso de detección binaria sin granularidad intencional.</t>
+          <t>Diferencia E2-E3: 0.25. El abstract sugería relevancia (0.55) pero el texto completo no confirmó intención comunicativa (0.3). Probable caso de detección binaria sin granularidad intencional.</t>
         </is>
       </c>
     </row>
@@ -8857,27 +8857,29 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>articulo_000910</t>
+          <t>articulo_000503</t>
         </is>
       </c>
       <c r="C11" s="15" t="n">
-        <v>2025</v>
+        <v>2021</v>
       </c>
       <c r="D11" s="16" t="inlineStr">
         <is>
-          <t>Disinformation and Misinformation in the Age of Generative AI</t>
+          <t>The Rise and Fall of Fake News sites: A Traffic Analysis</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
         <is>
-          <t>Koustav Rudra; Niloy Ganguly et al.</t>
+          <t>Manolis Chalkiadakis; Alexandros Kornilakis et al.</t>
         </is>
       </c>
       <c r="F11" s="15" t="n">
         <v>0.55</v>
       </c>
-      <c r="G11" s="15" t="n">
-        <v>0.25</v>
+      <c r="G11" s="15" t="inlineStr">
+        <is>
+          <t>N/D</t>
+        </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
@@ -8891,7 +8893,7 @@
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>Diferencia E2-E3: 0.3. El abstract sugería relevancia (0.55) pero el texto completo no confirmó intención comunicativa (0.25). Probable caso de detección binaria sin granularidad intencional.</t>
+          <t>Diferencia E2-E3: N/D. El abstract sugería relevancia (0.55) pero el texto completo no confirmó intención comunicativa (N/D). Probable caso de detección binaria sin granularidad intencional.</t>
         </is>
       </c>
     </row>
@@ -8901,29 +8903,27 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>articulo_000503</t>
+          <t>articulo_001622</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>The Rise and Fall of Fake News sites: A Traffic Analysis</t>
+          <t>Análisis cuantitativo y cualitativo de las falsas noticias sobre la COVID-19 en Colombia</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Manolis Chalkiadakis; Alexandros Kornilakis et al.</t>
+          <t>Lina María Leal Villamizar; Sonia Milena Torres Quiroga</t>
         </is>
       </c>
       <c r="F12" s="4" t="n">
         <v>0.55</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
+      <c r="G12" s="4" t="n">
+        <v>0.35</v>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
@@ -8937,7 +8937,7 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Diferencia E2-E3: N/D. El abstract sugería relevancia (0.55) pero el texto completo no confirmó intención comunicativa (N/D). Probable caso de detección binaria sin granularidad intencional.</t>
+          <t>Diferencia E2-E3: 0.2. El abstract sugería relevancia (0.55) pero el texto completo no confirmó intención comunicativa (0.35). Probable caso de detección binaria sin granularidad intencional.</t>
         </is>
       </c>
     </row>
@@ -8947,27 +8947,27 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>articulo_001622</t>
+          <t>articulo_000910</t>
         </is>
       </c>
       <c r="C13" s="15" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D13" s="16" t="inlineStr">
         <is>
-          <t>Análisis cuantitativo y cualitativo de las falsas noticias sobre la COVID-19 en Colombia</t>
+          <t>Disinformation and Misinformation in the Age of Generative AI</t>
         </is>
       </c>
       <c r="E13" s="15" t="inlineStr">
         <is>
-          <t>Lina María Leal Villamizar; Sonia Milena Torres Quiroga</t>
+          <t>Koustav Rudra; Niloy Ganguly et al.</t>
         </is>
       </c>
       <c r="F13" s="15" t="n">
         <v>0.55</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0.35</v>
+        <v>0.25</v>
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
@@ -8981,7 +8981,7 @@
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>Diferencia E2-E3: 0.2. El abstract sugería relevancia (0.55) pero el texto completo no confirmó intención comunicativa (0.35). Probable caso de detección binaria sin granularidad intencional.</t>
+          <t>Diferencia E2-E3: 0.3. El abstract sugería relevancia (0.55) pero el texto completo no confirmó intención comunicativa (0.25). Probable caso de detección binaria sin granularidad intencional.</t>
         </is>
       </c>
     </row>
@@ -8991,27 +8991,27 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>articulo_001675</t>
+          <t>articulo_001433</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>"We are not going back" VS "Make America Great Again." The Discourse of 2024 US Presidential Campaign</t>
+          <t>Adversarial Attacks against Neural Ranking Models via In-Context Learning</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Svitlana Kuranova; Pavlo Zernetskyi</t>
+          <t>Amin Bigdeli; Negar Arabzadeh et al.</t>
         </is>
       </c>
       <c r="F14" s="4" t="n">
         <v>0.55</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Diferencia E2-E3: 0.25. El abstract sugería relevancia (0.55) pero el texto completo no confirmó intención comunicativa (0.3). Probable caso de detección binaria sin granularidad intencional.</t>
+          <t>Diferencia E2-E3: 0.2. El abstract sugería relevancia (0.55) pero el texto completo no confirmó intención comunicativa (0.35). Probable caso de detección binaria sin granularidad intencional.</t>
         </is>
       </c>
     </row>
@@ -9035,27 +9035,27 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>articulo_001966</t>
+          <t>articulo_002036</t>
         </is>
       </c>
       <c r="C15" s="15" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="D15" s="16" t="inlineStr">
         <is>
-          <t>Strategic Use of Disinformation Terminology in Political Communication: Media Narratives of Delegitimisation</t>
+          <t>Euphemization in English Political Discourse: A Functional-Communicative Approach</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
         <is>
-          <t>María Jesús Fernández Torres; Nereida Cea et al.</t>
+          <t>Olga A. Zharina; Marina V. Samofalova et al.</t>
         </is>
       </c>
       <c r="F15" s="15" t="n">
         <v>0.52</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
@@ -9069,7 +9069,7 @@
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>Diferencia E2-E3: 0.27. El abstract sugería relevancia (0.52) pero el texto completo no confirmó intención comunicativa (0.25). Probable caso de detección binaria sin granularidad intencional.</t>
+          <t>Diferencia E2-E3: 0.22. El abstract sugería relevancia (0.52) pero el texto completo no confirmó intención comunicativa (0.3). Probable caso de detección binaria sin granularidad intencional.</t>
         </is>
       </c>
     </row>
@@ -9079,27 +9079,27 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>articulo_002036</t>
+          <t>articulo_001966</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Euphemization in English Political Discourse: A Functional-Communicative Approach</t>
+          <t>Strategic Use of Disinformation Terminology in Political Communication: Media Narratives of Delegitimisation</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Olga A. Zharina; Marina V. Samofalova et al.</t>
+          <t>María Jesús Fernández Torres; Nereida Cea et al.</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
         <v>0.52</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Diferencia E2-E3: 0.22. El abstract sugería relevancia (0.52) pero el texto completo no confirmó intención comunicativa (0.3). Probable caso de detección binaria sin granularidad intencional.</t>
+          <t>Diferencia E2-E3: 0.27. El abstract sugería relevancia (0.52) pero el texto completo no confirmó intención comunicativa (0.25). Probable caso de detección binaria sin granularidad intencional.</t>
         </is>
       </c>
     </row>
@@ -9123,20 +9123,20 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>articulo_000686</t>
+          <t>articulo_000673</t>
         </is>
       </c>
       <c r="C17" s="15" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D17" s="16" t="inlineStr">
         <is>
-          <t>Tweets similarity classification based on Machine Learning Algorithms, TF-IDF and the Dynamic Case Based Reasoning</t>
+          <t>An Awareness About Phishing Attack And Fake News Using Machine Learning Technique</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
         <is>
-          <t>Mohamed Kouissi; El Mokhtar En-Naimi et al.</t>
+          <t>Kripakrishna R K; Clara Kanmani. A</t>
         </is>
       </c>
       <c r="F17" s="15" t="n">
@@ -9167,20 +9167,20 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>articulo_000673</t>
+          <t>articulo_000920</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>An Awareness About Phishing Attack And Fake News Using Machine Learning Technique</t>
+          <t>Combat Greenwashing with GoalSpotter: Automatic Sustainability Objective Detection in Heterogeneous Reports</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Kripakrishna R K; Clara Kanmani. A</t>
+          <t>Mohammad Mahdavi; Ramin Baghaei Mehr et al.</t>
         </is>
       </c>
       <c r="F18" s="4" t="n">
@@ -9211,20 +9211,20 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>articulo_000920</t>
+          <t>articulo_000983</t>
         </is>
       </c>
       <c r="C19" s="15" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D19" s="16" t="inlineStr">
         <is>
-          <t>Combat Greenwashing with GoalSpotter: Automatic Sustainability Objective Detection in Heterogeneous Reports</t>
+          <t>Computational Approaches to the Detection of Lesser-Known Rhetorical Figures: A Systematic Survey and Research Challenges</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
         <is>
-          <t>Mohammad Mahdavi; Ramin Baghaei Mehr et al.</t>
+          <t>Ramona Kühn; Jelena Mitrović et al.</t>
         </is>
       </c>
       <c r="F19" s="15" t="n">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>articulo_003194</t>
+          <t>articulo_000810</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
@@ -9263,12 +9263,12 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Fake it till you make it: the psychological and communication tactics behind "Pig Butchering" scams</t>
+          <t>A Novel Approach for Distinguishing Human and AI-Generated Texts</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Ayşe Nur Asyalı; Muriel-Larissa Frank et al.</t>
+          <t>Ahmed Abdulhamed; Prabhat Ranjan et al.</t>
         </is>
       </c>
       <c r="F20" s="4" t="n">
@@ -9299,27 +9299,27 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>articulo_000983</t>
+          <t>articulo_003194</t>
         </is>
       </c>
       <c r="C21" s="15" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D21" s="16" t="inlineStr">
         <is>
-          <t>Computational Approaches to the Detection of Lesser-Known Rhetorical Figures: A Systematic Survey and Research Challenges</t>
+          <t>Fake it till you make it: the psychological and communication tactics behind "Pig Butchering" scams</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
         <is>
-          <t>Ramona Kühn; Jelena Mitrović et al.</t>
+          <t>Ayşe Nur Asyalı; Muriel-Larissa Frank et al.</t>
         </is>
       </c>
       <c r="F21" s="15" t="n">
         <v>0.45</v>
       </c>
       <c r="G21" s="15" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H21" s="15" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>Diferencia E2-E3: 0.1. El abstract sugería relevancia (0.45) pero el texto completo no confirmó intención comunicativa (0.35). Probable caso de detección binaria sin granularidad intencional.</t>
+          <t>Diferencia E2-E3: 0.15. El abstract sugería relevancia (0.45) pero el texto completo no confirmó intención comunicativa (0.3). Probable caso de detección binaria sin granularidad intencional.</t>
         </is>
       </c>
     </row>
@@ -9343,27 +9343,27 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>articulo_000810</t>
+          <t>articulo_000686</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2026</v>
+        <v>2023</v>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>A Novel Approach for Distinguishing Human and AI-Generated Texts</t>
+          <t>Tweets similarity classification based on Machine Learning Algorithms, TF-IDF and the Dynamic Case Based Reasoning</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Ahmed Abdulhamed; Prabhat Ranjan et al.</t>
+          <t>Mohamed Kouissi; El Mokhtar En-Naimi et al.</t>
         </is>
       </c>
       <c r="F22" s="4" t="n">
         <v>0.45</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Diferencia E2-E3: 0.15. El abstract sugería relevancia (0.45) pero el texto completo no confirmó intención comunicativa (0.3). Probable caso de detección binaria sin granularidad intencional.</t>
+          <t>Diferencia E2-E3: 0.1. El abstract sugería relevancia (0.45) pero el texto completo no confirmó intención comunicativa (0.35). Probable caso de detección binaria sin granularidad intencional.</t>
         </is>
       </c>
     </row>
@@ -9387,27 +9387,27 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>articulo_001417</t>
+          <t>articulo_000964</t>
         </is>
       </c>
       <c r="C23" s="15" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D23" s="16" t="inlineStr">
         <is>
-          <t>Breaking the News: Taking the Roles of Influencer vs. Journalist in a LLM-Based Game for Raising Misinformation Awareness</t>
+          <t>Advancing Misinformation Awareness in Recommender Systems for Social Media Information Integrity</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
         <is>
-          <t>Huiyun Tang; Songqi Sun et al.</t>
+          <t>Royal Pathak</t>
         </is>
       </c>
       <c r="F23" s="15" t="n">
         <v>0.4</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>Diferencia E2-E3: 0.1. El abstract sugería relevancia (0.4) pero el texto completo no confirmó intención comunicativa (0.3). Probable caso de detección binaria sin granularidad intencional.</t>
+          <t>Diferencia E2-E3: 0.05. El abstract sugería relevancia (0.4) pero el texto completo no confirmó intención comunicativa (0.35). Probable caso de detección binaria sin granularidad intencional.</t>
         </is>
       </c>
     </row>
@@ -9431,27 +9431,27 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>articulo_001471</t>
+          <t>articulo_000589</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Much Ado about Disinformation: A Critical Approach to Coping with Information Manipulation in a Post-Truth World</t>
+          <t>Machine Learning-Assisted Public Opinion Segmentation and Diversified Policy Response Mechanism</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Dong-ha Seo</t>
+          <t>Sinian Chen</t>
         </is>
       </c>
       <c r="F24" s="4" t="n">
         <v>0.4</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
@@ -9465,7 +9465,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Diferencia E2-E3: 0.3. El abstract sugería relevancia (0.4) pero el texto completo no confirmó intención comunicativa (0.1). Probable caso de detección binaria sin granularidad intencional.</t>
+          <t>Diferencia E2-E3: 0.2. El abstract sugería relevancia (0.4) pero el texto completo no confirmó intención comunicativa (0.2). Probable caso de detección binaria sin granularidad intencional.</t>
         </is>
       </c>
     </row>
@@ -9475,27 +9475,27 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>articulo_001523</t>
+          <t>articulo_001471</t>
         </is>
       </c>
       <c r="C25" s="15" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="D25" s="16" t="inlineStr">
         <is>
-          <t>The Definition and Typological Model of a Dogwhistle</t>
+          <t>Much Ado about Disinformation: A Critical Approach to Coping with Information Manipulation in a Post-Truth World</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
         <is>
-          <t>Kimberly Witten</t>
+          <t>Dong-ha Seo</t>
         </is>
       </c>
       <c r="F25" s="15" t="n">
         <v>0.4</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H25" s="15" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>Diferencia E2-E3: 0.1. El abstract sugería relevancia (0.4) pero el texto completo no confirmó intención comunicativa (0.3). Probable caso de detección binaria sin granularidad intencional.</t>
+          <t>Diferencia E2-E3: 0.3. El abstract sugería relevancia (0.4) pero el texto completo no confirmó intención comunicativa (0.1). Probable caso de detección binaria sin granularidad intencional.</t>
         </is>
       </c>
     </row>
@@ -9519,27 +9519,27 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>articulo_001625</t>
+          <t>articulo_000996</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Periodismo, política y falsedad en las noticias durante campaña electoral presidencial de 1930 en Colombia</t>
+          <t>When Journalism Meets AI: Risk or Opportunity?</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Álvaro Acevedo Tarazona; Melissa Quiroz Prada et al.</t>
+          <t>Sophia Cheng</t>
         </is>
       </c>
       <c r="F26" s="4" t="n">
         <v>0.4</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Diferencia E2-E3: 0.25. El abstract sugería relevancia (0.4) pero el texto completo no confirmó intención comunicativa (0.15). Probable caso de detección binaria sin granularidad intencional.</t>
+          <t>Diferencia E2-E3: 0.1. El abstract sugería relevancia (0.4) pero el texto completo no confirmó intención comunicativa (0.3). Probable caso de detección binaria sin granularidad intencional.</t>
         </is>
       </c>
     </row>
@@ -9563,27 +9563,27 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>articulo_000589</t>
+          <t>articulo_001625</t>
         </is>
       </c>
       <c r="C27" s="15" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D27" s="16" t="inlineStr">
         <is>
-          <t>Machine Learning-Assisted Public Opinion Segmentation and Diversified Policy Response Mechanism</t>
+          <t>Periodismo, política y falsedad en las noticias durante campaña electoral presidencial de 1930 en Colombia</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
-          <t>Sinian Chen</t>
+          <t>Álvaro Acevedo Tarazona; Melissa Quiroz Prada et al.</t>
         </is>
       </c>
       <c r="F27" s="15" t="n">
         <v>0.4</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>Diferencia E2-E3: 0.2. El abstract sugería relevancia (0.4) pero el texto completo no confirmó intención comunicativa (0.2). Probable caso de detección binaria sin granularidad intencional.</t>
+          <t>Diferencia E2-E3: 0.25. El abstract sugería relevancia (0.4) pero el texto completo no confirmó intención comunicativa (0.15). Probable caso de detección binaria sin granularidad intencional.</t>
         </is>
       </c>
     </row>
@@ -9607,7 +9607,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>articulo_000927</t>
+          <t>articulo_001440</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
@@ -9615,19 +9615,19 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Multi-Level Text Importance Classification Architecture Based on Deep Learning</t>
+          <t>Fake news and the seven sins of capital: a metaphorical analysis of vices in the context of the COVID-19 pandemic</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Meizhen Huang; Jinshu Su et al.</t>
+          <t>Paulo R. Vasconcellos-Silva; Luis David Castiel</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
         <v>0.4</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Diferencia E2-E3: 0.2. El abstract sugería relevancia (0.4) pero el texto completo no confirmó intención comunicativa (0.2). Probable caso de detección binaria sin granularidad intencional.</t>
+          <t>Diferencia E2-E3: 0.1. El abstract sugería relevancia (0.4) pero el texto completo no confirmó intención comunicativa (0.3). Probable caso de detección binaria sin granularidad intencional.</t>
         </is>
       </c>
     </row>
@@ -9651,27 +9651,27 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>articulo_000679</t>
+          <t>articulo_000927</t>
         </is>
       </c>
       <c r="C29" s="15" t="n">
-        <v>2025</v>
+        <v>2022</v>
       </c>
       <c r="D29" s="16" t="inlineStr">
         <is>
-          <t>A Comprehensive Review of Fake News on Social Media and Its Influence on Modern Society</t>
+          <t>Multi-Level Text Importance Classification Architecture Based on Deep Learning</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
         <is>
-          <t>Neha Tyagi; Tanya Gupta et al.</t>
+          <t>Meizhen Huang; Jinshu Su et al.</t>
         </is>
       </c>
       <c r="F29" s="15" t="n">
         <v>0.4</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H29" s="15" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>Diferencia E2-E3: 0.1. El abstract sugería relevancia (0.4) pero el texto completo no confirmó intención comunicativa (0.3). Probable caso de detección binaria sin granularidad intencional.</t>
+          <t>Diferencia E2-E3: 0.2. El abstract sugería relevancia (0.4) pero el texto completo no confirmó intención comunicativa (0.2). Probable caso de detección binaria sin granularidad intencional.</t>
         </is>
       </c>
     </row>
@@ -9695,20 +9695,20 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>articulo_000993</t>
+          <t>articulo_001417</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Popups, Credibility, and the Spread of Misinformation</t>
+          <t>Breaking the News: Taking the Roles of Influencer vs. Journalist in a LLM-Based Game for Raising Misinformation Awareness</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Hollis Greenberg; Laurie Dringus et al.</t>
+          <t>Huiyun Tang; Songqi Sun et al.</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
@@ -9739,7 +9739,7 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>articulo_000964</t>
+          <t>articulo_000993</t>
         </is>
       </c>
       <c r="C31" s="15" t="n">
@@ -9747,19 +9747,19 @@
       </c>
       <c r="D31" s="16" t="inlineStr">
         <is>
-          <t>Advancing Misinformation Awareness in Recommender Systems for Social Media Information Integrity</t>
+          <t>Popups, Credibility, and the Spread of Misinformation</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
         <is>
-          <t>Royal Pathak</t>
+          <t>Hollis Greenberg; Laurie Dringus et al.</t>
         </is>
       </c>
       <c r="F31" s="15" t="n">
         <v>0.4</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="H31" s="15" t="inlineStr">
         <is>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>Diferencia E2-E3: 0.05. El abstract sugería relevancia (0.4) pero el texto completo no confirmó intención comunicativa (0.35). Probable caso de detección binaria sin granularidad intencional.</t>
+          <t>Diferencia E2-E3: 0.1. El abstract sugería relevancia (0.4) pero el texto completo no confirmó intención comunicativa (0.3). Probable caso de detección binaria sin granularidad intencional.</t>
         </is>
       </c>
     </row>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>articulo_000996</t>
+          <t>articulo_000679</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
@@ -9791,12 +9791,12 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>When Journalism Meets AI: Risk or Opportunity?</t>
+          <t>A Comprehensive Review of Fake News on Social Media and Its Influence on Modern Society</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Sophia Cheng</t>
+          <t>Neha Tyagi; Tanya Gupta et al.</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
@@ -9827,7 +9827,7 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>articulo_001910</t>
+          <t>articulo_001523</t>
         </is>
       </c>
       <c r="C33" s="15" t="n">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="D33" s="16" t="inlineStr">
         <is>
-          <t>PivotFEC: Enhancing Few-shot Factual Error Correction with a Pivot Task Approach using Large Language Models</t>
+          <t>The Definition and Typological Model of a Dogwhistle</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
         <is>
-          <t>Xingwei He; A-Long Jin et al.</t>
+          <t>Kimberly Witten</t>
         </is>
       </c>
       <c r="F33" s="15" t="n">
@@ -9871,20 +9871,20 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>articulo_001440</t>
+          <t>articulo_001910</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Fake news and the seven sins of capital: a metaphorical analysis of vices in the context of the COVID-19 pandemic</t>
+          <t>PivotFEC: Enhancing Few-shot Factual Error Correction with a Pivot Task Approach using Large Language Models</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Paulo R. Vasconcellos-Silva; Luis David Castiel</t>
+          <t>Xingwei He; A-Long Jin et al.</t>
         </is>
       </c>
       <c r="F34" s="4" t="n">
@@ -14610,7 +14610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -14691,7 +14691,7 @@
       </c>
       <c r="D2" s="7" t="inlineStr">
         <is>
-          <t>Modality Deep-learning Frameworks for Fake News Detection on Social Networks</t>
+          <t>Modality Deep-learning Frameworks for Fake News Detection on Social Networks: A Systematic Literature Review</t>
         </is>
       </c>
       <c r="E2" s="6" t="n">
@@ -14737,7 +14737,7 @@
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>A Survey on Automatic Credibility Assessment Using Textual Credibility Signals</t>
+          <t>A Survey on Automatic Credibility Assessment Using Textual Credibility Signals in the Era of LLMs</t>
         </is>
       </c>
       <c r="E3" s="6" t="n">
@@ -14770,50 +14770,48 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n">
+      <c r="A4" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>articulo_001967</t>
         </is>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="6" t="n">
         <v>2023</v>
       </c>
-      <c r="D4" s="16" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Enabling Contextual Soft Moderation on Social Media through Contrastive Textual Deviation</t>
         </is>
       </c>
-      <c r="E4" s="15" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="F4" s="15" t="inlineStr">
-        <is>
-          <t>N/D</t>
-        </is>
-      </c>
-      <c r="G4" s="15" t="inlineStr">
+      <c r="E4" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H4" s="15" t="inlineStr">
-        <is>
-          <t>Indeterminado</t>
-        </is>
-      </c>
-      <c r="I4" s="16" t="inlineStr">
-        <is>
-          <t>Sin patrón predefinido.</t>
-        </is>
-      </c>
-      <c r="J4" s="16" t="inlineStr">
-        <is>
-          <t>Revisión caso por caso.</t>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Adyacente</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="inlineStr">
+        <is>
+          <t>LLM sobre-relevó el artículo. Detectó intención comunicativa en metadatos; evaluador humano juzgó relevancia media tras análisis crítico.</t>
+        </is>
+      </c>
+      <c r="J4" s="7" t="inlineStr">
+        <is>
+          <t>Se mantiene decisión LLM como criterio operativo del pipeline. La discrepancia adyacente es aceptable en sistemas de cribado asistido.</t>
         </is>
       </c>
     </row>
@@ -14877,7 +14875,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>DisTrack: a new Tool for Semi-automatic Misinformation Tracking</t>
+          <t>DisTrack: a new Tool for Semi-automatic Misinformation Tracking in Online Social Networks</t>
         </is>
       </c>
       <c r="E6" s="6" t="n">
@@ -15015,7 +15013,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>A systematic review on media bias detection</t>
+          <t>A systematic review on media bias detection: What is media bias, how it is expressed, and how to detect it</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
@@ -15140,94 +15138,94 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>articulo_003331</t>
-        </is>
-      </c>
-      <c r="C12" s="15" t="n">
+      <c r="A12" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>articulo_001602</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>Muertes de celebridades: Sobre la clasificación automática de noticias falsas no intencionadas</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Adyacente</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>LLM sub-relevó. El evaluador humano identificó granularidad intencional explícita que el LLM no ponderó suficientemente.</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Se mantiene decisión LLM como criterio operativo del pipeline. La discrepancia adyacente es aceptable en sistemas de cribado asistido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>articulo_001635</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
         <v>2022</v>
       </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>In-context annotation of topic-oriented datasets of fake news</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Asustar para desestabilizar: desinformación sobre la COVID-19 en Argentina y España</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="G12" s="15" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H12" s="15" t="inlineStr">
-        <is>
-          <t>Indeterminado</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>Sin patrón predefinido.</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>Revisión caso por caso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>articulo_000146</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="n">
-        <v>2023</v>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>Using Deep Learning Models to Detect Fake News about COVID-19</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="F13" s="15" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G13" s="15" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H13" s="15" t="inlineStr">
-        <is>
-          <t>Indeterminado</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>Sin patrón predefinido.</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>Revisión caso por caso.</t>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>Adyacente</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>LLM sub-relevó. El evaluador humano identificó granularidad intencional explícita que el LLM no ponderó suficientemente.</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Se mantiene decisión LLM como criterio operativo del pipeline. La discrepancia adyacente es aceptable en sistemas de cribado asistido.</t>
         </is>
       </c>
     </row>
@@ -15278,94 +15276,94 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n">
-        <v>23</v>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>articulo_003259</t>
-        </is>
-      </c>
-      <c r="C15" s="15" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>An Improved Multiple Features and ML-Based Approach for Detecting Clickbait News</t>
-        </is>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="A15" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>articulo_000691</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>2025</v>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Multilevel Annotation Model for Detecting Fake News in Kazakh-Language Media</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Adyacente</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>LLM sub-relevó. El evaluador humano identificó granularidad intencional explícita que el LLM no ponderó suficientemente.</t>
+        </is>
+      </c>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Se mantiene decisión LLM como criterio operativo del pipeline. La discrepancia adyacente es aceptable en sistemas de cribado asistido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>articulo_000555</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>GPT Assisted Annotation of Rhetorical and Linguistic Features for Interpretable Propaganda Technique Detection</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="H15" s="15" t="inlineStr">
-        <is>
-          <t>Indeterminado</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>Sin patrón predefinido.</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>Revisión caso por caso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="n">
-        <v>25</v>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>articulo_003396</t>
-        </is>
-      </c>
-      <c r="C16" s="15" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>To share or not to share - motives of sharing fake news amidst COVID-19 Malaysia</t>
-        </is>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F16" s="15" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="G16" s="15" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="H16" s="15" t="inlineStr">
-        <is>
-          <t>Indeterminado</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>Sin patrón predefinido.</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>Revisión caso por caso.</t>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Adyacente</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>LLM sub-relevó. El evaluador humano identificó granularidad intencional explícita que el LLM no ponderó suficientemente.</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Se mantiene decisión LLM como criterio operativo del pipeline. La discrepancia adyacente es aceptable en sistemas de cribado asistido.</t>
         </is>
       </c>
     </row>
@@ -15383,7 +15381,7 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>XAI in Automated Fact-Checking? The Benefits Are Modest</t>
+          <t>XAI in Automated Fact-Checking? The Benefits Are Modest and There's No One-Explanation-Fits-All</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
@@ -15429,7 +15427,7 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>A Perturbation-Theoretic Model for Fact-Checker Deployment</t>
+          <t>A Perturbation-Theoretic Model for Fact-Checker Deployment in Dynamic Disinformation Networks</t>
         </is>
       </c>
       <c r="E18" s="6" t="n">
@@ -15456,6 +15454,52 @@
         </is>
       </c>
       <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Se mantiene decisión LLM como criterio operativo del pipeline. La discrepancia adyacente es aceptable en sistemas de cribado asistido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>articulo_001003</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>The fake news effect: what does it mean for consumer behavioral intentions towards brands?</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>Adyacente</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>LLM infra-detectó. Artículo con componente de intención comunicativa que el evaluador reconoció como relevante.</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Se mantiene decisión LLM como criterio operativo del pipeline. La discrepancia adyacente es aceptable en sistemas de cribado asistido.</t>
         </is>
